--- a/turkish_notes.xlsx
+++ b/turkish_notes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="135" windowWidth="22035" windowHeight="12090" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="135" windowWidth="22035" windowHeight="12090" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">vocab_turkish!$C$1:$D$594</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
